--- a/uploads/HRIS.xlsx
+++ b/uploads/HRIS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://venturecorplk-my.sharepoint.com/personal/sandalis_venturecorplk_com/Documents/Desktop/Company Folder/3 Collective RCM Pvt Ltd/TOT/2026/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\new user\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="27" documentId="13_ncr:1_{48FA7030-06C2-4C10-8E51-35436DC4DFA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CE1C8D1D-E8AB-42C3-82AA-66A1EBA9E545}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D77EB280-07D5-4823-8D46-70D59C1AA71E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="13776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026" sheetId="1" r:id="rId1"/>
@@ -203,8 +203,8 @@
     <numFmt numFmtId="164" formatCode="#,##0.00;[Red]#,##0.00"/>
     <numFmt numFmtId="165" formatCode="#,##0.0"/>
     <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
-    <numFmt numFmtId="169" formatCode="000000000000"/>
-    <numFmt numFmtId="170" formatCode="[$-409]d/mmm/yyyy;@"/>
+    <numFmt numFmtId="167" formatCode="000000000000"/>
+    <numFmt numFmtId="168" formatCode="[$-409]d/mmm/yyyy;@"/>
   </numFmts>
   <fonts count="9" x14ac:knownFonts="1">
     <font>
@@ -509,13 +509,13 @@
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="1" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -530,7 +530,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -554,7 +554,7 @@
     <xf numFmtId="166" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1">
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
     <xf numFmtId="3" fontId="2" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -621,6 +621,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -643,9 +646,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -954,13 +954,13 @@
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.6640625" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="35.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.109375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="16.88671875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="17" style="14" customWidth="1"/>
+    <col min="2" max="2" width="11.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.6640625" style="1" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="22.44140625" style="1" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="4.88671875" style="1" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="19.109375" style="1" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="16.88671875" style="1" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="17" style="14" hidden="1" customWidth="1"/>
     <col min="9" max="9" width="12.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="14.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="16.109375" style="1" bestFit="1" customWidth="1"/>
@@ -1014,25 +1014,25 @@
       <c r="F1" s="3"/>
       <c r="G1" s="3"/>
       <c r="H1" s="12"/>
-      <c r="I1" s="50" t="s">
+      <c r="I1" s="51" t="s">
         <v>0</v>
       </c>
-      <c r="J1" s="50"/>
-      <c r="K1" s="50"/>
-      <c r="L1" s="50"/>
-      <c r="M1" s="55" t="s">
+      <c r="J1" s="51"/>
+      <c r="K1" s="51"/>
+      <c r="L1" s="51"/>
+      <c r="M1" s="56" t="s">
         <v>1</v>
       </c>
-      <c r="N1" s="55"/>
-      <c r="O1" s="55"/>
-      <c r="P1" s="55"/>
-      <c r="Q1" s="55"/>
-      <c r="R1" s="55"/>
-      <c r="S1" s="55"/>
-      <c r="T1" s="55"/>
-      <c r="U1" s="55"/>
-      <c r="V1" s="55"/>
-      <c r="W1" s="56" t="s">
+      <c r="N1" s="56"/>
+      <c r="O1" s="56"/>
+      <c r="P1" s="56"/>
+      <c r="Q1" s="56"/>
+      <c r="R1" s="56"/>
+      <c r="S1" s="56"/>
+      <c r="T1" s="56"/>
+      <c r="U1" s="56"/>
+      <c r="V1" s="56"/>
+      <c r="W1" s="57" t="s">
         <v>2</v>
       </c>
       <c r="X1" s="29"/>
@@ -1125,7 +1125,7 @@
       <c r="V2" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="W2" s="57"/>
+      <c r="W2" s="58"/>
       <c r="X2" s="30" t="s">
         <v>23</v>
       </c>
@@ -1192,14 +1192,14 @@
       <c r="AS2" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="AT2" s="53" t="s">
+      <c r="AT2" s="54" t="s">
         <v>39</v>
       </c>
-      <c r="AU2" s="54"/>
-      <c r="AV2" s="51" t="s">
+      <c r="AU2" s="55"/>
+      <c r="AV2" s="52" t="s">
         <v>40</v>
       </c>
-      <c r="AW2" s="52"/>
+      <c r="AW2" s="53"/>
     </row>
     <row r="3" spans="1:50" s="16" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="17" t="s">
@@ -1236,20 +1236,20 @@
         <v>100000</v>
       </c>
       <c r="M3" s="20">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="N3" s="21">
         <v>30000</v>
       </c>
       <c r="O3" s="21">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="P3" s="21">
         <f t="shared" ref="P3:P4" si="1">INT(L3/62)</f>
         <v>1612</v>
       </c>
       <c r="Q3" s="21">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="R3" s="20">
         <v>17378</v>
@@ -1261,41 +1261,41 @@
         <v>60000</v>
       </c>
       <c r="U3" s="21">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="V3" s="21">
         <f t="shared" ref="V3:V4" si="2">SUM(M3:U3)</f>
-        <v>118990</v>
+        <v>158990</v>
       </c>
       <c r="W3" s="21">
         <f t="shared" ref="W3:W4" si="3">L3+V3</f>
-        <v>218990</v>
+        <v>258990</v>
       </c>
       <c r="X3" s="22">
         <v>31</v>
       </c>
       <c r="Y3" s="23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z3" s="23">
         <f>X3-Y3</f>
-        <v>31</v>
+        <v>-969</v>
       </c>
       <c r="AA3" s="24">
         <f t="shared" ref="AA3:AA4" si="4">(I3/X3)*Z3</f>
-        <v>40000</v>
+        <v>-1250322.5806451612</v>
       </c>
       <c r="AB3" s="25">
         <f t="shared" ref="AB3:AB4" si="5">(J3/X3)*Z3</f>
-        <v>10000</v>
+        <v>-312580.6451612903</v>
       </c>
       <c r="AC3" s="25">
         <f t="shared" ref="AC3:AC4" si="6">(K3/X3)*Z3</f>
-        <v>50000</v>
+        <v>-1562903.2258064516</v>
       </c>
       <c r="AD3" s="25">
         <f t="shared" ref="AD3:AD4" si="7">(M3/X3)*Z3</f>
-        <v>0</v>
+        <v>-312580.6451612903</v>
       </c>
       <c r="AE3" s="25">
         <f t="shared" ref="AE3:AE4" si="8">N3</f>
@@ -1303,7 +1303,7 @@
       </c>
       <c r="AF3" s="24">
         <f t="shared" ref="AF3:AF4" si="9">O3</f>
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AG3" s="25">
         <f t="shared" ref="AG3:AG4" si="10">R3</f>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="AI3" s="21">
         <f t="shared" ref="AI3:AI4" si="12">Q3</f>
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AJ3" s="21">
         <f t="shared" ref="AJ3:AJ4" si="13">S3</f>
@@ -1326,52 +1326,52 @@
         <v>60000</v>
       </c>
       <c r="AL3" s="25">
-        <f t="shared" ref="AL3:AL4" si="15">U3</f>
+        <f>U3</f>
+        <v>10000</v>
+      </c>
+      <c r="AM3" s="24">
+        <f t="shared" ref="AM3:AM4" si="15">AA3+AC3+AD3+AB3+AE3+AF3+AG3+AH3+AI3+AJ3+AK3+AL3</f>
+        <v>-3289397.0967741935</v>
+      </c>
+      <c r="AN3" s="24">
+        <f t="shared" ref="AN3:AN4" si="16">AM3</f>
+        <v>-3289397.0967741935</v>
+      </c>
+      <c r="AO3" s="49">
+        <f t="shared" ref="AO3" si="17">IF(AN3&lt;=150000, 0, IF(AN3&lt;=228333,AN3* 6.38%-9570, IF(AN3&lt;=262500,AN3* 21.95%-45119, IF(AN3&lt;=294167,AN3* 31.58%-70398, IF(AN3&lt;=323333,AN3* 42.86%-103580,AN3* 56.25%-146875)))))</f>
         <v>0</v>
       </c>
-      <c r="AM3" s="24">
-        <f t="shared" ref="AM3:AM4" si="16">AA3+AC3+AD3+AB3+AE3+AF3+AG3+AH3+AI3+AJ3+AK3+AL3</f>
-        <v>218990</v>
-      </c>
-      <c r="AN3" s="24">
-        <f t="shared" ref="AN3:AN4" si="17">AM3</f>
-        <v>218990</v>
-      </c>
-      <c r="AO3" s="49">
-        <f t="shared" ref="AO3" si="18">IF(AN3&lt;=150000, 0, IF(AN3&lt;=228333,AN3* 6.38%-9570, IF(AN3&lt;=262500,AN3* 21.95%-45119, IF(AN3&lt;=294167,AN3* 31.58%-70398, IF(AN3&lt;=323333,AN3* 42.86%-103580,AN3* 56.25%-146875)))))</f>
-        <v>4401.5619999999999</v>
-      </c>
       <c r="AP3" s="24">
-        <f t="shared" ref="AP3:AP4" si="19">(AA3+AB3)*0.12</f>
-        <v>6000</v>
+        <f t="shared" ref="AP3:AP4" si="18">(AA3+AB3)*0.12</f>
+        <v>-187548.38709677415</v>
       </c>
       <c r="AQ3" s="25">
-        <f t="shared" ref="AQ3:AQ4" si="20">(AA3+AB3)*0.08</f>
-        <v>4000</v>
+        <f t="shared" ref="AQ3:AQ4" si="19">(AA3+AB3)*0.08</f>
+        <v>-125032.25806451612</v>
       </c>
       <c r="AR3" s="25">
-        <f t="shared" ref="AR3:AR4" si="21">AP3+AQ3</f>
-        <v>10000</v>
+        <f t="shared" ref="AR3:AR4" si="20">AP3+AQ3</f>
+        <v>-312580.6451612903</v>
       </c>
       <c r="AS3" s="24">
-        <f t="shared" ref="AS3:AS4" si="22">(AA3+AB3)*0.03</f>
-        <v>1500</v>
+        <f t="shared" ref="AS3:AS4" si="21">(AA3+AB3)*0.03</f>
+        <v>-46887.096774193538</v>
       </c>
       <c r="AT3" s="25">
-        <f t="shared" ref="AT3:AT4" si="23">AN3-AQ3</f>
-        <v>214990</v>
+        <f t="shared" ref="AT3:AT4" si="22">AN3-AQ3</f>
+        <v>-3164364.8387096776</v>
       </c>
       <c r="AU3" s="26">
-        <f t="shared" ref="AU3:AU4" si="24">AT3/300</f>
-        <v>716.63333333333333</v>
+        <f t="shared" ref="AU3:AU4" si="23">AT3/300</f>
+        <v>-10547.882795698924</v>
       </c>
       <c r="AV3" s="45">
-        <f t="shared" ref="AV3:AV4" si="25">AM3+AO3+AP3+AS3</f>
-        <v>230891.56200000001</v>
+        <f t="shared" ref="AV3:AV4" si="24">AM3+AO3+AP3+AS3</f>
+        <v>-3523832.5806451612</v>
       </c>
       <c r="AW3" s="43">
-        <f t="shared" ref="AW3:AW4" si="26">AV3/300</f>
-        <v>769.63854000000003</v>
+        <f t="shared" ref="AW3:AW4" si="25">AV3/300</f>
+        <v>-11746.108602150538</v>
       </c>
       <c r="AX3" s="27"/>
     </row>
@@ -1500,67 +1500,67 @@
         <v>25000</v>
       </c>
       <c r="AL4" s="25">
+        <f t="shared" ref="AL3:AL4" si="26">U4</f>
+        <v>0</v>
+      </c>
+      <c r="AM4" s="24">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="AM4" s="24">
+        <v>139547</v>
+      </c>
+      <c r="AN4" s="24">
         <f t="shared" si="16"/>
         <v>139547</v>
       </c>
-      <c r="AN4" s="24">
-        <f t="shared" si="17"/>
-        <v>139547</v>
-      </c>
       <c r="AO4" s="49">
         <v>0</v>
       </c>
       <c r="AP4" s="24">
+        <f t="shared" si="18"/>
+        <v>4800</v>
+      </c>
+      <c r="AQ4" s="25">
         <f t="shared" si="19"/>
-        <v>4800</v>
-      </c>
-      <c r="AQ4" s="25">
+        <v>3200</v>
+      </c>
+      <c r="AR4" s="25">
         <f t="shared" si="20"/>
-        <v>3200</v>
-      </c>
-      <c r="AR4" s="25">
+        <v>8000</v>
+      </c>
+      <c r="AS4" s="24">
         <f t="shared" si="21"/>
-        <v>8000</v>
-      </c>
-      <c r="AS4" s="24">
+        <v>1200</v>
+      </c>
+      <c r="AT4" s="25">
         <f t="shared" si="22"/>
-        <v>1200</v>
-      </c>
-      <c r="AT4" s="25">
+        <v>136347</v>
+      </c>
+      <c r="AU4" s="26">
         <f t="shared" si="23"/>
-        <v>136347</v>
-      </c>
-      <c r="AU4" s="26">
+        <v>454.49</v>
+      </c>
+      <c r="AV4" s="45">
         <f t="shared" si="24"/>
-        <v>454.49</v>
-      </c>
-      <c r="AV4" s="45">
+        <v>145547</v>
+      </c>
+      <c r="AW4" s="46">
         <f t="shared" si="25"/>
-        <v>145547</v>
-      </c>
-      <c r="AW4" s="46">
-        <f t="shared" si="26"/>
         <v>485.15666666666669</v>
       </c>
       <c r="AX4" s="27"/>
     </row>
     <row r="5" spans="1:50" x14ac:dyDescent="0.3">
-      <c r="M5" s="58" t="s">
+      <c r="M5" s="50" t="s">
         <v>51</v>
       </c>
-      <c r="N5" s="58"/>
-      <c r="O5" s="58"/>
-      <c r="P5" s="58"/>
-      <c r="Q5" s="58"/>
-      <c r="R5" s="58"/>
-      <c r="S5" s="58"/>
-      <c r="T5" s="58"/>
-      <c r="U5" s="58"/>
-      <c r="V5" s="58"/>
+      <c r="N5" s="50"/>
+      <c r="O5" s="50"/>
+      <c r="P5" s="50"/>
+      <c r="Q5" s="50"/>
+      <c r="R5" s="50"/>
+      <c r="S5" s="50"/>
+      <c r="T5" s="50"/>
+      <c r="U5" s="50"/>
+      <c r="V5" s="50"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:AX4" xr:uid="{00000000-0001-0000-0000-000000000000}">

--- a/uploads/HRIS.xlsx
+++ b/uploads/HRIS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\new user\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D77EB280-07D5-4823-8D46-70D59C1AA71E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{595CC450-FFD8-47F6-98BF-992885C23AB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="13776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026" sheetId="1" r:id="rId1"/>
@@ -1500,7 +1500,7 @@
         <v>25000</v>
       </c>
       <c r="AL4" s="25">
-        <f t="shared" ref="AL3:AL4" si="26">U4</f>
+        <f t="shared" ref="AL4" si="26">U4</f>
         <v>0</v>
       </c>
       <c r="AM4" s="24">
